--- a/results/Int Task Remove ACC 0.3/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_2_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6318036010754975</v>
+        <v>0.6283077579940131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6276867597621716</v>
+        <v>0.6263911947609176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6311647466644658</v>
+        <v>0.6213803540761292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6302100362837562</v>
+        <v>0.6147866623071135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6308310345155976</v>
+        <v>0.6109856769634654</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6358740163229286</v>
+        <v>0.6119261024008228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6358740163229286</v>
+        <v>0.6091119685604269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6254471980877223</v>
+        <v>0.6109606783125989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5961297326810935</v>
+        <v>0.6024718507255165</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6193352263528635</v>
+        <v>0.6024718507255165</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6152148138036995</v>
+        <v>0.5815809146807951</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.611718970722215</v>
+        <v>0.5777406457429282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5710414041146985</v>
+        <v>0.5649226867121457</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5701045499131794</v>
+        <v>0.5655829685382059</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5817662221403924</v>
+        <v>0.533767225260859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6054625623379055</v>
+        <v>0.5197338556331881</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6228917804435952</v>
+        <v>0.5291881073084945</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6187713678944311</v>
+        <v>0.5247589812613287</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6061014167489374</v>
+        <v>0.5200532828387039</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6048094229835215</v>
+        <v>0.5149567324938019</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6154985286508348</v>
+        <v>0.5181224346622564</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6192673728719402</v>
+        <v>0.5215825653853601</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6230790719231025</v>
+        <v>0.5269199757473406</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6211803648691976</v>
+        <v>0.5437246243853506</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6381973036375814</v>
+        <v>0.5446757635302222</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6379635860921791</v>
+        <v>0.5381249265912633</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6594310783227573</v>
+        <v>0.5220519844960748</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6515168229016212</v>
+        <v>0.499188932660777</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6515168229016212</v>
+        <v>0.4976203665199022</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.623700070154944</v>
+        <v>0.4941709495043125</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6132839656272518</v>
+        <v>0.4982413647517435</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6127629619988763</v>
+        <v>0.4776857280718184</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.645271128224826</v>
+        <v>0.4595748007250403</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6657910525463706</v>
+        <v>0.4727407568480431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6505692549925877</v>
+        <v>0.4727407568480431</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6505692549925877</v>
+        <v>0.4424042988156195</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6527802467803325</v>
+        <v>0.4625762260449436</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6559209502979204</v>
+        <v>0.4391243171003469</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6654144855674455</v>
+        <v>0.4163021360751959</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6562296637959222</v>
+        <v>0.4197551243266236</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6537099585101757</v>
+        <v>0.4326409368383294</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6439077097426489</v>
+        <v>0.4247695362472502</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.69362010621649</v>
+        <v>0.4336385020490958</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6977012351714351</v>
+        <v>0.4126832837592892</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6499069891466175</v>
+        <v>0.4114341448239301</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6293620661742064</v>
+        <v>0.4073494446331468</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6163976864740632</v>
+        <v>0.4104008672547831</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6492931333864521</v>
+        <v>0.4662252354634829</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6474015688042233</v>
+        <v>0.4728689245342315</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6035083027265196</v>
+        <v>0.4665732325557033</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6187765263461972</v>
+        <v>0.4566301183745639</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.56472587193707</v>
+        <v>0.4647959475202926</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5319875594015562</v>
+        <v>0.4647959475202926</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5421592326763318</v>
+        <v>0.4663823698403578</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5317466993844776</v>
+        <v>0.4601259614560484</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5016868137275131</v>
+        <v>0.461680242653571</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5007892431202126</v>
+        <v>0.4303640755895713</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4998666738620455</v>
+        <v>0.4401663243570982</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5040656535996471</v>
+        <v>0.416196983019964</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.476584597021748</v>
+        <v>0.4306406479650304</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4251841964084478</v>
+        <v>0.4290720818241556</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4251841964084478</v>
+        <v>0.4424824692000749</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4512073951564519</v>
+        <v>0.4291808061152255</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4838226984575436</v>
+        <v>0.3043649231628769</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4662954697682982</v>
+        <v>0.4152053698689277</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4680068853426957</v>
+        <v>0.4152053698689277</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5339386445810861</v>
+        <v>0.4493285283016472</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5729849500185704</v>
+        <v>0.3816460698946406</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5725996533520413</v>
+        <v>0.3620308586520727</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5451023278108801</v>
+        <v>0.3629927115044585</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6151759270134628</v>
+        <v>0.4129102556369973</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6161342086300104</v>
+        <v>0.3881790506544092</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6088730925632585</v>
+        <v>0.3872421964528898</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6072973839507074</v>
+        <v>0.406764555563668</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5045743563045804</v>
+        <v>0.4247326334769235</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5045743563045804</v>
+        <v>0.4245147880908015</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5045743563045804</v>
+        <v>0.3961234631781777</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4440744467758883</v>
+        <v>0.511334308942057</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4504237072919874</v>
+        <v>0.4539739125190069</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.510566096432891</v>
+        <v>0.4526890612252672</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5042525482751725</v>
+        <v>0.4561634768917233</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5042525482751725</v>
+        <v>0.4646344482996156</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5077198214699524</v>
+        <v>0.4360217067650317</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5102538116990512</v>
+        <v>0.4152125123406039</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4645173911249234</v>
+        <v>0.4962930572000877</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4942237244339194</v>
+        <v>0.4959772012304098</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4932725852890479</v>
+        <v>0.4953490605268922</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4939007259925655</v>
+        <v>0.4950153483780241</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4939007259925655</v>
+        <v>0.4956506315532178</v>
       </c>
     </row>
   </sheetData>
